--- a/public/files/Nike_EHQ_30pct_ruling_overview.xlsx
+++ b/public/files/Nike_EHQ_30pct_ruling_overview.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated for the SD Worx hackathon demo</t>
+          <t>Generated for the SDWorx hackathon demo</t>
         </is>
       </c>
     </row>
